--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -529,15 +529,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -554,20 +555,25 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>표시명 (조건 문구용 — 선행 해금을 이름으로 보여 준다)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>지불 골드 (0=조건 없음)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>계정 레벨 요구치 (0=조건 없음)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>선행 해금 TID 목록 (쉼표 · 빈 셀=없음 · 전부 열려야 함)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>설명 (메모 — 로직 미사용)</t>
         </is>
@@ -604,6 +610,11 @@
           <t>a</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -618,20 +629,25 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -646,14 +662,15 @@
       <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -666,6 +683,7 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -676,12 +694,13 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -696,12 +715,13 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -712,20 +732,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AccountLevel</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>RequiredUnlockTIDs</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -735,13 +760,18 @@
       <c r="B10" t="n">
         <v>1002</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>작업슬롯 2번</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>500</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>작업슬롯 2번 · 골드는 테스트값 · 계정 레벨은 곡선 확정 뒤 채운다</t>
         </is>
@@ -751,18 +781,23 @@
       <c r="B11" t="n">
         <v>1003</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>작업슬롯 3번</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>1500</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
@@ -772,18 +807,23 @@
       <c r="B12" t="n">
         <v>1004</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>작업슬롯 4번</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>4000</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
@@ -793,18 +833,23 @@
       <c r="B13" t="n">
         <v>1005</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>작업슬롯 5번</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10000</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
@@ -814,18 +859,23 @@
       <c r="B14" t="n">
         <v>1006</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>작업슬롯 6번</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>25000</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
@@ -835,18 +885,23 @@
       <c r="B15" t="n">
         <v>1007</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>작업슬롯 7번</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>60000</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>작업슬롯 7번 · 상한</t>
         </is>
@@ -863,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A2:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -872,7 +927,6 @@
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
@@ -1042,7 +1096,6 @@
       <c r="C12" t="n">
         <v>1002</v>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" t="n">
@@ -1051,7 +1104,6 @@
       <c r="C13" t="n">
         <v>1003</v>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" t="n">
@@ -1060,7 +1112,6 @@
       <c r="C14" t="n">
         <v>1004</v>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" t="n">
@@ -1069,7 +1120,6 @@
       <c r="C15" t="n">
         <v>1005</v>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" t="n">
@@ -1078,7 +1128,6 @@
       <c r="C16" t="n">
         <v>1006</v>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="n">

--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -75,7 +75,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -100,8 +100,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -124,11 +129,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -163,6 +182,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -238,6 +272,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>해금 TID (슬롯 1xxx · 산업레벨 2xxx · 특성 3xxx)</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>표시명 (조건 문구용 — 선행 해금을 이름으로 보여 준다)</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>지불 골드 (0=조건 없음)</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>계정 레벨 요구치 (0=조건 없음)</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>선행 해금 TID 목록 (쉼표 · 빈 셀=없음 · 전부 열려야 함)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>작업슬롯 번호 (= TID · 행 수가 곧 상한)</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>이 칸을 여는 해금 (0=항상 열림)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,7 +613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -532,12 +621,12 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -548,34 +637,34 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>해금 TID (슬롯 1xxx · 산업레벨 2xxx · 특성 3xxx)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>표시명 (조건 문구용 — 선행 해금을 이름으로 보여 준다)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>지불 골드 (0=조건 없음)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>계정 레벨 요구치 (0=조건 없음)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>선행 해금 TID 목록 (쉼표 · 빈 셀=없음 · 전부 열려야 함)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>해금 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>표시명</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>지불 골드</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>요구 계정 Lv</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>선행 해금</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -585,32 +674,32 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -622,32 +711,32 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -659,18 +748,18 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -678,12 +767,12 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -691,16 +780,16 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -712,196 +801,196 @@
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>UnlockTID</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>AccountLevel</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>RequiredUnlockTIDs</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="16" t="n">
         <v>1002</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 2번</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="16" t="n">
         <v>500</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 2번 · 골드는 테스트값 · 계정 레벨은 곡선 확정 뒤 채운다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="16" t="n">
         <v>1003</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="16" t="n">
         <v>1500</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="16" t="n">
         <v>1004</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="16" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="16" t="n">
         <v>1005</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="16" t="n">
         <v>10000</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="16" t="n">
         <v>1006</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="16" t="n">
         <v>25000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="16" t="n">
         <v>1007</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 7번</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="16" t="n">
         <v>60000</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>작업슬롯 7번 · 상한</t>
         </is>
@@ -909,43 +998,45 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>작업슬롯 번호 (= TID · 행 수가 곧 상한)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>이 칸을 여는 해금 (0=항상 열림)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>슬롯 번호</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>여는 해금</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
@@ -955,17 +1046,17 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>a</t>
         </is>
@@ -977,17 +1068,17 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -999,13 +1090,13 @@
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1013,9 +1104,9 @@
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1023,9 +1114,9 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -1037,106 +1128,106 @@
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>WorkSlotTID</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>UnlockTID</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>시작 칸</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>시작 칸</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="16" t="n">
         <v>1002</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="16" t="n">
         <v>1003</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="16" t="n">
         <v>1004</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="16" t="n">
         <v>1005</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="16" t="n">
         <v>1006</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="16" t="n">
         <v>1007</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>상한</t>
         </is>
@@ -1144,5 +1235,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -74,8 +74,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -105,8 +128,13 @@
         <fgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -143,11 +171,12 @@
         <color indexed="64"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,6 +226,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,367 +684,382 @@
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="24" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="24" t="n"/>
+      <c r="F1" s="24" t="n"/>
+      <c r="G1" s="24" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>해금 TID</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>표시명</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>지불 골드</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>요구 계정 Lv</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>선행 해금</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n">
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n"/>
+      <c r="G8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>UnlockTID</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>AccountLevel</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>RequiredUnlockTIDs</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="22" t="n">
         <v>1002</v>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 2번</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="22" t="n">
         <v>500</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 2번 · 골드는 테스트값 · 계정 레벨은 곡선 확정 뒤 채운다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="22" t="n">
         <v>1003</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="22" t="n">
         <v>1500</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="22" t="n">
         <v>1004</v>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="22" t="n">
         <v>1005</v>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>1004</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="24" t="n"/>
+      <c r="B14" s="22" t="n">
         <v>1006</v>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="22" t="n">
         <v>25000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="n">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="22" t="n">
         <v>1007</v>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 7번</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>1006</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 7번 · 상한</t>
         </is>
@@ -1017,217 +1086,235 @@
     <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="24" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>슬롯 번호</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>여는 해금</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="n"/>
+      <c r="D5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
+      <c r="B6" s="20" t="n"/>
+      <c r="C6" s="20" t="n"/>
+      <c r="D6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n"/>
+      <c r="D8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>WorkSlotTID</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>UnlockTID</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="16" t="n">
+      <c r="A10" s="24" t="n"/>
+      <c r="B10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>시작 칸</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="n">
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>시작 칸</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="24" t="n"/>
+      <c r="B12" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="22" t="n">
         <v>1002</v>
       </c>
+      <c r="D12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="24" t="n"/>
+      <c r="B13" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="22" t="n">
         <v>1003</v>
       </c>
+      <c r="D13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="24" t="n"/>
+      <c r="B14" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="22" t="n">
         <v>1004</v>
       </c>
+      <c r="D14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="n">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="22" t="n">
         <v>1005</v>
       </c>
+      <c r="D15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="n">
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="22" t="n">
         <v>1006</v>
       </c>
+      <c r="D16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="n">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="22" t="n">
         <v>1007</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>상한</t>
         </is>

--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -7,7 +7,6 @@
   </bookViews>
   <sheets>
     <sheet name="UnlockTable" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="WorkSlotTable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -357,26 +356,6 @@
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
         <t>선행 해금 TID 목록 (쉼표 · 빈 셀=없음 · 전부 열려야 함)</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>excel-table-creator</author>
-  </authors>
-  <commentList>
-    <comment ref="B2" authorId="0" shapeId="0">
-      <text>
-        <t>작업슬롯 번호 (= TID · 행 수가 곧 상한)</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="0" shapeId="0">
-      <text>
-        <t>이 칸을 여는 해금 (0=항상 열림)</t>
       </text>
     </comment>
   </commentList>
@@ -672,12 +651,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
@@ -1065,258 +1044,1178 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="n"/>
-      <c r="B1" s="24" t="n"/>
-      <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>//</t>
-        </is>
-      </c>
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>슬롯 번호</t>
-        </is>
-      </c>
-      <c r="C2" s="19" t="inlineStr">
-        <is>
-          <t>여는 해금</t>
-        </is>
-      </c>
-      <c r="D2" s="19" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>C&amp;S</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="20" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>Default(Null)</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>UnlockTable.UnlockTID?</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="26" t="n"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>WorkSlotTID</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>UnlockTID</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>시작 칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="n"/>
-      <c r="B11" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>시작 칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="n"/>
-      <c r="B12" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>1002</v>
-      </c>
-      <c r="D12" s="24" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="n"/>
-      <c r="B13" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>1003</v>
-      </c>
-      <c r="D13" s="24" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n"/>
-      <c r="B14" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>1004</v>
-      </c>
-      <c r="D14" s="24" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n"/>
-      <c r="B15" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>1005</v>
-      </c>
-      <c r="D15" s="24" t="n"/>
-    </row>
     <row r="16">
       <c r="A16" s="24" t="n"/>
       <c r="B16" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>1006</v>
-      </c>
-      <c r="D16" s="24" t="n"/>
+        <v>2102</v>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>농사 Lv2</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="n"/>
       <c r="B17" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>1007</v>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>상한</t>
+        <v>2103</v>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>농사 Lv3</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="22" t="n">
+        <v>2104</v>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>농사 Lv4</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="22" t="n">
+        <v>2105</v>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>농사 Lv5</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>2104</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="22" t="n">
+        <v>2202</v>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>낚시 Lv2</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="22" t="n">
+        <v>2203</v>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>낚시 Lv3</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="22" t="n">
+        <v>2204</v>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>낚시 Lv4</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="22" t="n">
+        <v>2205</v>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>낚시 Lv5</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="22" t="n">
+        <v>2302</v>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>채굴 Lv2</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="24" t="n"/>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="22" t="n">
+        <v>2303</v>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>채굴 Lv3</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="22" t="n">
+        <v>2304</v>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>채굴 Lv4</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="22" t="n">
+        <v>2305</v>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>채굴 Lv5</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="22" t="n">
+        <v>2402</v>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>벌목 Lv2</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="22" t="n">
+        <v>2403</v>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>벌목 Lv3</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>2402</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="22" t="n">
+        <v>2404</v>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>벌목 Lv4</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="22" t="n">
+        <v>2405</v>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>벌목 Lv5</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="22" t="n">
+        <v>2502</v>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>사냥 Lv2</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="24" t="n"/>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="22" t="n">
+        <v>2503</v>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>사냥 Lv3</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="22" t="n">
+        <v>2504</v>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>사냥 Lv4</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="22" t="n">
+        <v>2505</v>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>사냥 Lv5</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="22" t="n">
+        <v>3101</v>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>농사 속도 10%</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="24" t="n"/>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="22" t="n">
+        <v>3102</v>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>농사 속도 20%</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="22" t="n">
+        <v>3103</v>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>농사 속도 30%</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="22" t="n">
+        <v>3104</v>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>농사 속도 40%</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="22" t="n">
+        <v>3105</v>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>농사 속도 50%</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="22" t="n">
+        <v>3201</v>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>낚시 속도 10%</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="24" t="n"/>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="22" t="n">
+        <v>3202</v>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>낚시 속도 20%</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n"/>
+      <c r="B43" s="22" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>낚시 속도 30%</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="22" t="n">
+        <v>3204</v>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>낚시 속도 40%</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="22" t="n">
+        <v>3205</v>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>낚시 속도 50%</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n"/>
+      <c r="B46" s="22" t="n">
+        <v>3301</v>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>채굴 속도 10%</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="24" t="n"/>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="22" t="n">
+        <v>3302</v>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>채굴 속도 20%</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="22" t="n">
+        <v>3303</v>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>채굴 속도 30%</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="n"/>
+      <c r="B49" s="22" t="n">
+        <v>3304</v>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>채굴 속도 40%</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="22" t="n">
+        <v>3305</v>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>채굴 속도 50%</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n"/>
+      <c r="B51" s="22" t="n">
+        <v>3401</v>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>벌목 속도 10%</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="24" t="n"/>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="n"/>
+      <c r="B52" s="22" t="n">
+        <v>3402</v>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>벌목 속도 20%</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>3401</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="n"/>
+      <c r="B53" s="22" t="n">
+        <v>3403</v>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>벌목 속도 30%</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="n"/>
+      <c r="B54" s="22" t="n">
+        <v>3404</v>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>벌목 속도 40%</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n"/>
+      <c r="B55" s="22" t="n">
+        <v>3405</v>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>벌목 속도 50%</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="n"/>
+      <c r="B56" s="22" t="n">
+        <v>3501</v>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>사냥 속도 10%</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="24" t="n"/>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="n"/>
+      <c r="B57" s="22" t="n">
+        <v>3502</v>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>사냥 속도 20%</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="n"/>
+      <c r="B58" s="22" t="n">
+        <v>3503</v>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>사냥 속도 30%</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n"/>
+      <c r="B59" s="22" t="n">
+        <v>3504</v>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>사냥 속도 40%</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="n"/>
+      <c r="B60" s="22" t="n">
+        <v>3505</v>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>사냥 속도 50%</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>특성 노드 — 특성 포인트로만 연다</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -646,7 +646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -660,7 +660,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D10" s="22" t="n">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="E10" s="22" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
       <c r="F10" s="24" t="n"/>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>작업슬롯 2번 · 골드는 테스트값 · 계정 레벨은 곡선 확정 뒤 채운다</t>
+          <t>작업슬롯 2번 · 골드 단독 해금(계정 레벨 조건 없음)</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="D11" s="22" t="n">
-        <v>1500</v>
+        <v>30000</v>
       </c>
       <c r="E11" s="22" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>4000</v>
+        <v>300000</v>
       </c>
       <c r="E12" s="22" t="n">
         <v>0</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D13" s="22" t="n">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
       <c r="E13" s="22" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D14" s="22" t="n">
-        <v>25000</v>
+        <v>5000000</v>
       </c>
       <c r="E14" s="22" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="D15" s="22" t="n">
-        <v>60000</v>
+        <v>10000000</v>
       </c>
       <c r="E15" s="22" t="n">
         <v>0</v>
@@ -2221,6 +2221,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -646,7 +646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -759,7 +759,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -1046,6 +1046,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Unlock.xlsx
+++ b/GameDesign/Excel/Unlock.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -92,6 +92,14 @@
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -175,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +258,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,16 +668,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,6 +690,8 @@
       <c r="E1" s="24" t="n"/>
       <c r="F1" s="24" t="n"/>
       <c r="G1" s="24" t="n"/>
+      <c r="H1" s="24" t="n"/>
+      <c r="I1" s="24" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
@@ -705,6 +726,16 @@
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
+          <t>자원 비용</t>
+        </is>
+      </c>
+      <c r="H2" s="27" t="inlineStr">
+        <is>
+          <t>자원 수량</t>
+        </is>
+      </c>
+      <c r="I2" s="27" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -745,6 +776,16 @@
           <t>a</t>
         </is>
       </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
@@ -779,6 +820,16 @@
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="H4" s="28" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="I4" s="28" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -801,6 +852,8 @@
       </c>
       <c r="F5" s="20" t="n"/>
       <c r="G5" s="20" t="n"/>
+      <c r="H5" s="28" t="n"/>
+      <c r="I5" s="28" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
@@ -814,6 +867,8 @@
       <c r="E6" s="20" t="n"/>
       <c r="F6" s="20" t="n"/>
       <c r="G6" s="20" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="28" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
@@ -835,6 +890,16 @@
           <t>""</t>
         </is>
       </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
@@ -851,7 +916,13 @@
           <t>UnlockTable.UnlockTID?</t>
         </is>
       </c>
-      <c r="G8" s="20" t="n"/>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>ItemTable.ItemTID?</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="26" t="n"/>
@@ -881,6 +952,16 @@
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>ItemTIDs</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>ItemCounts</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -903,7 +984,9 @@
         <v>0</v>
       </c>
       <c r="F10" s="24" t="n"/>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 2번 · 골드 단독 해금(계정 레벨 조건 없음)</t>
         </is>
@@ -930,7 +1013,9 @@
           <t>1002</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 3번</t>
         </is>
@@ -957,7 +1042,9 @@
           <t>1003</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 4번</t>
         </is>
@@ -984,7 +1071,9 @@
           <t>1004</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 5번</t>
         </is>
@@ -1011,7 +1100,9 @@
           <t>1005</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 6번</t>
         </is>
@@ -1038,9 +1129,1101 @@
           <t>1006</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>작업슬롯 7번 · 상한</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n"/>
+      <c r="B16" s="22" t="n">
+        <v>4101</v>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>농장 Lv1</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>농장 짓기 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="22" t="n">
+        <v>4102</v>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>농장 Lv2</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>20001,20002</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>200,20</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>농장 Lv2 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="22" t="n">
+        <v>4103</v>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>농장 Lv3</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>농장 Lv3 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="22" t="n">
+        <v>4111</v>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>농장 작업속도 I</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +3% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="22" t="n">
+        <v>4112</v>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>농장 산출량 I</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>4111,4102</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 산출량 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="22" t="n">
+        <v>4113</v>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>농장 작업속도 II</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>4112,4103</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>20002</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n"/>
+      <c r="B22" s="22" t="n">
+        <v>4201</v>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 Lv1</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="24" t="n"/>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 짓기 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n"/>
+      <c r="B23" s="22" t="n">
+        <v>4202</v>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 Lv2</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>10001,10002</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>200,20</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 Lv2 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n"/>
+      <c r="B24" s="22" t="n">
+        <v>4203</v>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 Lv3</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 Lv3 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="22" t="n">
+        <v>4211</v>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 작업속도 I</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +3% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="22" t="n">
+        <v>4212</v>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 산출량 I</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>4211,4202</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 산출량 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="22" t="n">
+        <v>4213</v>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>발굴 캠프 작업속도 II</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>4212,4203</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="22" t="n">
+        <v>4301</v>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>광산 Lv1</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>광산 짓기 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="22" t="n">
+        <v>4302</v>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>광산 Lv2</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>40001,40002</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>200,20</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>광산 Lv2 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="22" t="n">
+        <v>4303</v>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>광산 Lv3</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>4302,4402</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>40002,30001</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>100,200</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>광산 Lv3 · 다른 건물 Lv2 선행 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n"/>
+      <c r="B31" s="22" t="n">
+        <v>4311</v>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>광산 작업속도 I</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +3% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n"/>
+      <c r="B32" s="22" t="n">
+        <v>4312</v>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>광산 산출량 I</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>4311,4302</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>40002</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 산출량 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n"/>
+      <c r="B33" s="22" t="n">
+        <v>4313</v>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>광산 작업속도 II</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>4312,4303</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>40002</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I33" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n"/>
+      <c r="B34" s="22" t="n">
+        <v>4401</v>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>제재소 Lv1</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="24" t="n"/>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>제재소 짓기 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n"/>
+      <c r="B35" s="22" t="n">
+        <v>4402</v>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>제재소 Lv2</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>30001,30002</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>200,20</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>제재소 Lv2 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n"/>
+      <c r="B36" s="22" t="n">
+        <v>4403</v>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>제재소 Lv3</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>4402,4302</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>30002,40001</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>100,200</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>제재소 Lv3 · 다른 건물 Lv2 선행 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n"/>
+      <c r="B37" s="22" t="n">
+        <v>4411</v>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>제재소 작업속도 I</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>4401</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>30001</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +3% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n"/>
+      <c r="B38" s="22" t="n">
+        <v>4412</v>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>제재소 산출량 I</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>4411,4402</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>30002</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 산출량 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n"/>
+      <c r="B39" s="22" t="n">
+        <v>4413</v>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>제재소 작업속도 II</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>4412,4403</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>30002</t>
+        </is>
+      </c>
+      <c r="H39" s="23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n"/>
+      <c r="B40" s="22" t="n">
+        <v>4501</v>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 Lv1</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="24" t="n"/>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>50001</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 짓기 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n"/>
+      <c r="B41" s="22" t="n">
+        <v>4502</v>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 Lv2</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>4501</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>50001,50002</t>
+        </is>
+      </c>
+      <c r="H41" s="23" t="inlineStr">
+        <is>
+          <t>200,20</t>
+        </is>
+      </c>
+      <c r="I41" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 Lv2 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n"/>
+      <c r="B42" s="22" t="n">
+        <v>4503</v>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 Lv3</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 Lv3 (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n"/>
+      <c r="B43" s="22" t="n">
+        <v>4511</v>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 작업속도 I</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>4501</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>50001</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +3% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n"/>
+      <c r="B44" s="22" t="n">
+        <v>4512</v>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 산출량 I</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>4511,4502</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 산출량 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n"/>
+      <c r="B45" s="22" t="n">
+        <v>4513</v>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>사냥꾼 오두막 작업속도 II</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>4512,4503</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="H45" s="23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I45" s="23" t="inlineStr">
+        <is>
+          <t>노드 · 속도 +5% (테스트값)</t>
         </is>
       </c>
     </row>
